--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486403_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486403_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0615</v>
+        <v>2.7585</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7167</v>
+        <v>3.5062</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6552</v>
+        <v>-0.7477</v>
       </c>
       <c r="G2" t="n">
         <v>3.6647</v>
@@ -610,13 +610,13 @@
         <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2982</v>
+        <v>-0.6011</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1043</v>
+        <v>-0.3148</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1939</v>
+        <v>-0.2863</v>
       </c>
       <c r="V2" t="n">
         <v>0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9681</v>
+        <v>2.2707</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1969</v>
+        <v>0.2222</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7711</v>
+        <v>2.0485</v>
       </c>
       <c r="G3" t="n">
         <v>0.6475</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0155</v>
+        <v>0.3182</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0601</v>
+        <v>0.0853</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0446</v>
+        <v>0.2328</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8797</v>
+        <v>2.1804</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3002</v>
+        <v>1.9707</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5796</v>
+        <v>0.2097</v>
       </c>
       <c r="G4" t="n">
         <v>0.9379</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3632</v>
+        <v>-0.0625</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.0709</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3783</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9546</v>
+        <v>-0.1358</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2393</v>
+        <v>1.0966</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2847</v>
+        <v>-1.2324</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1573</v>
+        <v>1.0323</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1836</v>
+        <v>-0.7089</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0263</v>
+        <v>1.7412</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4719</v>
+        <v>2.2166</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.1987</v>
+        <v>0.073</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7267</v>
+        <v>2.1436</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6854</v>
+        <v>-1.1843</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0151</v>
+        <v>-0.7819</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7004</v>
+        <v>-0.4024</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>-0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3071</v>
+        <v>-0.733</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5813</v>
+        <v>-0.0324</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2741</v>
+        <v>-0.7006</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6513</v>
+        <v>-0.7526</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5629</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2324</v>
+        <v>-1.3155</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0323</v>
+        <v>-2.1573</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7089</v>
+        <v>-2.1836</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7412</v>
+        <v>0.0263</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2166</v>
+        <v>-1.4719</v>
       </c>
       <c r="K6" t="n">
-        <v>0.073</v>
+        <v>-2.1987</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1436</v>
+        <v>0.7267</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1843</v>
+        <v>-0.6854</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7819</v>
+        <v>0.0151</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4024</v>
+        <v>-0.7004</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2486</v>
+        <v>0.6</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.548</v>
+        <v>0.9049</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7006</v>
+        <v>-0.3049</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1249</v>
+        <v>-1.8596</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8791</v>
+        <v>-0.1451</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7542</v>
+        <v>-1.7145</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.9422</v>
+        <v>-4.4354</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.135</v>
+        <v>-3.0321</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8072</v>
+        <v>-1.4033</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.5851</v>
+        <v>-2.2191</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.0313</v>
+        <v>-2.0678</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5538</v>
+        <v>-0.1514</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3572</v>
+        <v>-2.2162</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1038</v>
+        <v>-0.9643</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2534</v>
+        <v>-1.2519</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1648</v>
+        <v>-0.402</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8158</v>
+        <v>0.1839</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.651</v>
+        <v>-0.5858</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>1.8902</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1563</v>
+        <v>-2.3231</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2568</v>
+        <v>-3.1697</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8995</v>
+        <v>0.8467</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.4354</v>
+        <v>-2.9422</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.0321</v>
+        <v>-2.135</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4033</v>
+        <v>-0.8072</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.2191</v>
+        <v>-2.5851</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.0678</v>
+        <v>-2.0313</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1514</v>
+        <v>-0.5538</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2162</v>
+        <v>-0.3572</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9643</v>
+        <v>-0.1038</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2519</v>
+        <v>-0.2534</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6987</v>
+        <v>-0.0333</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0721</v>
+        <v>0.5252</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7708</v>
+        <v>-0.5585</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8902</v>
+        <v>0.1952</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7265</v>
+        <v>-3.0814</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0592</v>
+        <v>-2.8284</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3327</v>
+        <v>-0.2529</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3363</v>
@@ -1156,13 +1156,13 @@
         <v>2.8276</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5</v>
+        <v>0.1451</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1538</v>
+        <v>0.0769</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6538</v>
+        <v>0.0682</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3252</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.385</v>
+        <v>-3.187</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1742</v>
+        <v>-5.1611</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7892</v>
+        <v>1.9741</v>
       </c>
       <c r="G10" t="n">
         <v>-3.8282</v>
@@ -1234,13 +1234,13 @@
         <v>3.0451</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0772</v>
+        <v>0.1208</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6813</v>
+        <v>0.3317</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3959</v>
+        <v>-0.2109</v>
       </c>
       <c r="V10" t="n">
         <v>0.9554</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5322</v>
+        <v>-3.8701</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9989</v>
+        <v>-1.6758</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5333</v>
+        <v>-2.1942</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3332</v>
@@ -1312,13 +1312,13 @@
         <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.069</v>
+        <v>-1.4069</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4264</v>
+        <v>-0.1033</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6426</v>
+        <v>-1.3036</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.712299999999999</v>
+        <v>-7.999999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.334000000000001</v>
+        <v>-5.6215</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3783</v>
+        <v>-2.3782</v>
       </c>
       <c r="G12" t="n">
         <v>-12.7502</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.8698</v>
+        <v>-9.869800000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-2.8805</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7835999999999994</v>
+        <v>-0.7835999999999981</v>
       </c>
       <c r="K12" t="n">
         <v>-6.597</v>
@@ -1390,13 +1390,13 @@
         <v>17.4005</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.7675</v>
+        <v>-2.0547</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1258999999999997</v>
+        <v>1.5865</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.6414</v>
+        <v>-3.6412</v>
       </c>
       <c r="V12" t="n">
         <v>2.4552</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA ALCOLADO</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.6938</v>
+        <v>7.1491</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6584</v>
+        <v>5.8337</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0354</v>
+        <v>1.3154</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2386</v>
+        <v>5.8066</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3008</v>
+        <v>4.3308</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0623</v>
+        <v>1.4758</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1105</v>
+        <v>5.9741</v>
       </c>
       <c r="K13" t="n">
-        <v>2.881</v>
+        <v>3.142</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2295</v>
+        <v>2.8321</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1281</v>
+        <v>-0.1675</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4198</v>
+        <v>1.1888</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2917</v>
+        <v>-1.3563</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.2626</v>
+        <v>0.2175</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.7852</v>
+        <v>-1.305</v>
       </c>
       <c r="R13" t="n">
         <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4579</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4429</v>
+        <v>0.5997</v>
       </c>
       <c r="U13" t="n">
-        <v>1.015</v>
+        <v>-0.0397</v>
       </c>
       <c r="V13" t="n">
-        <v>2.2599</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8902</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8594</v>
+        <v>5.0681</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9397</v>
+        <v>3.7637</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9198</v>
+        <v>1.3045</v>
       </c>
       <c r="G14" t="n">
-        <v>5.8066</v>
+        <v>2.3514</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3308</v>
+        <v>2.5124</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4758</v>
+        <v>-0.161</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9741</v>
+        <v>3.1533</v>
       </c>
       <c r="K14" t="n">
-        <v>3.142</v>
+        <v>1.64</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8321</v>
+        <v>1.5133</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1675</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1888</v>
+        <v>0.8723</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3563</v>
+        <v>-1.6742</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5225</v>
+        <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7297</v>
+        <v>0.9337</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2944</v>
+        <v>0.6549</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4353</v>
+        <v>0.2788</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.1745</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>I. AURRECOECHEA ALCOLADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.939</v>
+        <v>4.3458</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7579</v>
+        <v>1.8703</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1812</v>
+        <v>2.4755</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3514</v>
+        <v>3.2386</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5124</v>
+        <v>4.3008</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.161</v>
+        <v>-1.0623</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1533</v>
+        <v>3.1105</v>
       </c>
       <c r="K15" t="n">
-        <v>1.64</v>
+        <v>2.881</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5133</v>
+        <v>0.2295</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8018999999999999</v>
+        <v>0.1281</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8723</v>
+        <v>1.4198</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6742</v>
+        <v>-1.2917</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9576</v>
+        <v>-3.2626</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.435</v>
+        <v>-4.7852</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1954</v>
+        <v>2.1099</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3509</v>
+        <v>1.6548</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1555</v>
+        <v>0.4551</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1745</v>
+        <v>2.2599</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3904</v>
+        <v>1.8902</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RUPÉREZ VÁZQUEZ</t>
+          <t>G. RENFROE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0048</v>
+        <v>0.7579</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0382</v>
+        <v>-1.7279</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0335</v>
+        <v>2.4858</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3028</v>
+        <v>1.4405</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1155</v>
+        <v>1.3958</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1873</v>
+        <v>0.0446</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0382</v>
+        <v>1.0095</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.5871</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0382</v>
+        <v>0.4224</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2645</v>
+        <v>0.4309</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1155</v>
+        <v>0.8087</v>
       </c>
       <c r="O16" t="n">
-        <v>0.149</v>
+        <v>-0.3778</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.6101</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.298</v>
+        <v>0.1875</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.1274</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.298</v>
+        <v>0.3148</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RENFROE</t>
+          <t>A. RUPÉREZ VÁZQUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.185</v>
+        <v>0.0048</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3985</v>
+        <v>0.0382</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2135</v>
+        <v>-0.0335</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4405</v>
+        <v>0.3028</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3958</v>
+        <v>0.1155</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0446</v>
+        <v>0.1873</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0095</v>
+        <v>0.0382</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5871</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4224</v>
+        <v>0.0382</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4309</v>
+        <v>0.2645</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8087</v>
+        <v>0.1155</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3778</v>
+        <v>0.149</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.87</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.6101</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7554</v>
+        <v>-0.298</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0425</v>
+        <v>-0.298</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4251</v>
+        <v>-0.4521</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2522</v>
+        <v>-1.5874</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.1353</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4099</v>
@@ -1858,13 +1858,13 @@
         <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3425</v>
+        <v>-0.3695</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0156</v>
+        <v>-0.3196</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3581</v>
+        <v>-0.0499</v>
       </c>
       <c r="V18" t="n">
         <v>-0.7602</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9796</v>
+        <v>-2.1225</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1646</v>
+        <v>-0.8358</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1442</v>
+        <v>-1.2867</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6042999999999999</v>
+        <v>0.2731</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5812</v>
+        <v>0.45</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9769</v>
+        <v>-0.1769</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8567</v>
+        <v>0.113</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6599</v>
+        <v>0.0365</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8032</v>
+        <v>0.0765</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2524</v>
+        <v>0.1601</v>
       </c>
       <c r="N19" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.4136</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1737</v>
+        <v>-0.2534</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>-0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.435</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6872</v>
+        <v>-0.3957</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4563</v>
+        <v>-0.0565</v>
       </c>
       <c r="U19" t="n">
-        <v>0.231</v>
+        <v>-0.3392</v>
       </c>
       <c r="V19" t="n">
-        <v>-4.1501</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.1501</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4257</v>
+        <v>-2.1464</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8358</v>
+        <v>-4.9117</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5899</v>
+        <v>2.7654</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2731</v>
+        <v>0.3515</v>
       </c>
       <c r="H20" t="n">
-        <v>0.45</v>
+        <v>-1.2103</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1769</v>
+        <v>1.5619</v>
       </c>
       <c r="J20" t="n">
-        <v>0.113</v>
+        <v>-0.3949</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0365</v>
+        <v>-2.1011</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0765</v>
+        <v>1.7061</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1601</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4136</v>
+        <v>0.8907</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2534</v>
+        <v>-0.1443</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.87</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-5.6552</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6988</v>
+        <v>0.265</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0565</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6423</v>
+        <v>0.2565</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>0.9347</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7695</v>
+        <v>-2.1473</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.694</v>
+        <v>-0.0648</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9246</v>
+        <v>-2.0826</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3515</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2103</v>
+        <v>-1.5812</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5619</v>
+        <v>0.9769</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3949</v>
+        <v>-0.8567</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.1011</v>
+        <v>-1.6599</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7061</v>
+        <v>0.8032</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.2524</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8907</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1443</v>
+        <v>0.1737</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.6976</v>
+        <v>1.0875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.6552</v>
+        <v>-0.435</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3581</v>
+        <v>1.5195</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7739</v>
+        <v>1.2269</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4158</v>
+        <v>0.2926</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9347</v>
+        <v>-4.1501</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>-4.1501</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>9.7121</v>
+        <v>10.4574</v>
       </c>
       <c r="E22" t="n">
-        <v>2.3783</v>
+        <v>2.378300000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>7.334</v>
+        <v>8.0791</v>
       </c>
       <c r="G22" t="n">
         <v>12.7503</v>
@@ -2146,22 +2146,22 @@
         <v>11.9667</v>
       </c>
       <c r="K22" t="n">
-        <v>3.272699999999999</v>
+        <v>3.2727</v>
       </c>
       <c r="L22" t="n">
         <v>8.693899999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7835000000000002</v>
+        <v>0.7835000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>6.5968</v>
+        <v>6.596800000000001</v>
       </c>
       <c r="O22" t="n">
         <v>-5.8133</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.3501</v>
+        <v>-4.350099999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-17.4005</v>
@@ -2170,13 +2170,13 @@
         <v>13.0504</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7672</v>
+        <v>4.5124</v>
       </c>
       <c r="T22" t="n">
         <v>3.6412</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1260999999999999</v>
+        <v>0.871</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4552</v>
